--- a/data/trans_orig/IP11A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11A-Estudios-trans_orig.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -3718,47 +3718,47 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4022,49 +4022,49 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
+          <t>15066</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>42,67%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>15188</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>43,02%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>9944</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>21,37%</t>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -7772,12 +7772,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>35053</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>543</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9776,12 +9776,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9932,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10797,12 +10797,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11253,12 +11253,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -11522,12 +11522,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -11635,12 +11635,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -11748,12 +11748,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13461,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -13569,12 +13569,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13697,12 +13697,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13732,12 +13732,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13767,12 +13767,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -13795,12 +13795,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13880,12 +13880,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -14590,12 +14590,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14886,12 +14886,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -15385,12 +15385,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15400,12 +15400,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15420,12 +15420,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15435,12 +15435,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15455,12 +15455,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -15498,12 +15498,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15513,12 +15513,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15548,12 +15548,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -15611,12 +15611,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15626,12 +15626,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15646,12 +15646,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15661,12 +15661,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15681,12 +15681,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -15724,12 +15724,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15739,12 +15739,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15759,12 +15759,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15794,12 +15794,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
